--- a/XLOOKUP Excel Tutorial File.xlsx
+++ b/XLOOKUP Excel Tutorial File.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/manaschintawar/Downloads/Microsoft Excel Project/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16B2FEC5-8607-A645-A7A7-DA12CFB5A406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A346816B-0DD0-7047-9190-FB3E8E88BDBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="4" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" activeTab="6" xr2:uid="{5EA44D8F-79D3-45F5-A0F6-C7F47358B7ED}"/>
   </bookViews>
   <sheets>
     <sheet name="XLookUp" sheetId="1" r:id="rId1"/>
@@ -2398,6 +2398,10 @@
       <c r="A2" t="s">
         <v>70</v>
       </c>
+      <c r="B2">
+        <f>_xlfn.XLOOKUP(I1,H1:S1,H2:S2)</f>
+        <v>310</v>
+      </c>
       <c r="G2" t="s">
         <v>70</v>
       </c>
@@ -2442,6 +2446,10 @@
       <c r="A3" t="s">
         <v>71</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B4" si="0">_xlfn.XLOOKUP(I2,H2:S2,H3:S3)</f>
+        <v>40</v>
+      </c>
       <c r="G3" t="s">
         <v>71</v>
       </c>
@@ -2485,6 +2493,10 @@
     <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>84</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>118</v>
       </c>
       <c r="G4" t="s">
         <v>84</v>
@@ -2584,6 +2596,10 @@
       <c r="A2" t="s">
         <v>70</v>
       </c>
+      <c r="B2">
+        <f>_xlfn.XLOOKUP(I1,H1:S1,H2:S2)</f>
+        <v>310</v>
+      </c>
       <c r="G2" t="s">
         <v>70</v>
       </c>
@@ -2628,6 +2644,10 @@
       <c r="A3" t="s">
         <v>71</v>
       </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B4" si="0">_xlfn.XLOOKUP(I2,H2:S2,H3:S3)</f>
+        <v>40</v>
+      </c>
       <c r="G3" t="s">
         <v>71</v>
       </c>
@@ -2672,6 +2692,10 @@
       <c r="A4" t="s">
         <v>84</v>
       </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>118</v>
+      </c>
       <c r="G4" t="s">
         <v>84</v>
       </c>
@@ -2720,6 +2744,10 @@
     <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>70</v>
+      </c>
+      <c r="B7">
+        <f>SUM(_xlfn.XLOOKUP(I1,H1:S1,H2:S2):_xlfn.XLOOKUP(J1,H1:S1,H2:S2))</f>
+        <v>460</v>
       </c>
     </row>
   </sheetData>
@@ -2733,6 +2761,9 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="6" width="10.1640625" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.2">
@@ -2818,6 +2849,10 @@
       <c r="A3" t="s">
         <v>63</v>
       </c>
+      <c r="B3" t="str">
+        <f>VLOOKUP(A3,H2:P10,9,FALSE)</f>
+        <v>Dwight.Schrute@AOL.com</v>
+      </c>
       <c r="E3">
         <v>1002</v>
       </c>
@@ -2856,6 +2891,10 @@
       <c r="A4" t="s">
         <v>66</v>
       </c>
+      <c r="B4" t="str">
+        <f t="shared" ref="B4:B5" si="0">VLOOKUP(A4,H3:P11,9,FALSE)</f>
+        <v>Michael.Scott@DunderMifflin.com</v>
+      </c>
       <c r="E4">
         <v>1003</v>
       </c>
@@ -2893,6 +2932,10 @@
     <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>68</v>
+      </c>
+      <c r="B5" t="str">
+        <f t="shared" si="0"/>
+        <v>Stanley.Hudson@gmail.com</v>
       </c>
       <c r="E5">
         <v>1004</v>
